--- a/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>LMDCF</t>
   </si>
@@ -656,225 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
-        <v>100</v>
-      </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
-        <v>100</v>
-      </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
-        <v>100</v>
-      </c>
       <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
       <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
       <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>800</v>
       </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
+        <v>100</v>
+      </c>
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
+        <v>100</v>
+      </c>
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
-        <v>100</v>
-      </c>
       <c r="V8" s="3">
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -888,7 +895,7 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -900,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
@@ -912,19 +919,19 @@
         <v>100</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
@@ -933,126 +940,132 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>700</v>
       </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
-        <v>100</v>
-      </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>700</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <v>500</v>
       </c>
-      <c r="W10" s="3">
-        <v>100</v>
-      </c>
       <c r="X10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="3">
         <v>700</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
       <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
         <v>500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>800</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>400</v>
       </c>
       <c r="AD10" s="3">
         <v>400</v>
       </c>
       <c r="AE10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,34 +1113,34 @@
         <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
       </c>
       <c r="K12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
@@ -1144,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
@@ -1153,13 +1167,13 @@
         <v>100</v>
       </c>
       <c r="Y12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>8</v>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1273,11 +1293,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1297,23 +1317,23 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1321,11 +1341,11 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1333,11 +1353,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1600</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1399,16 +1422,16 @@
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1423,13 +1446,13 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB15" s="3">
         <v>300</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>200</v>
       </c>
       <c r="AC15" s="3">
         <v>200</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,22 +1496,23 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
-        <v>700</v>
-      </c>
       <c r="G17" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
@@ -1506,19 +1533,19 @@
         <v>300</v>
       </c>
       <c r="N17" s="3">
+        <v>300</v>
+      </c>
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-100</v>
-      </c>
-      <c r="R17" s="3">
-        <v>300</v>
       </c>
       <c r="S17" s="3">
         <v>300</v>
@@ -1530,126 +1557,132 @@
         <v>300</v>
       </c>
       <c r="V17" s="3">
+        <v>300</v>
+      </c>
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4900</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>600</v>
       </c>
       <c r="AB17" s="3">
         <v>600</v>
       </c>
       <c r="AC17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD17" s="3">
         <v>400</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>600</v>
       </c>
       <c r="AE17" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
-        <v>100</v>
-      </c>
       <c r="W18" s="3">
+        <v>100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>200</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,44 +1714,45 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1756,111 +1790,117 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>-100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-100</v>
       </c>
       <c r="G21" s="3">
         <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
       </c>
-      <c r="V21" s="3">
-        <v>100</v>
-      </c>
       <c r="W21" s="3">
+        <v>100</v>
+      </c>
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>400</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>200</v>
       </c>
       <c r="AD21" s="3">
         <v>200</v>
       </c>
       <c r="AE21" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1876,8 +1916,8 @@
       <c r="G22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-100</v>
       </c>
       <c r="G23" s="3">
         <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>100</v>
-      </c>
       <c r="W23" s="3">
+        <v>100</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
-        <v>100</v>
-      </c>
       <c r="AC23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
       </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2049,40 +2095,40 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2091,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2103,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2115,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,86 +2264,89 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>100</v>
-      </c>
       <c r="W26" s="3">
+        <v>100</v>
+      </c>
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3">
         <v>0</v>
       </c>
@@ -2302,88 +2354,91 @@
         <v>0</v>
       </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-100</v>
       </c>
       <c r="G27" s="3">
         <v>-100</v>
       </c>
       <c r="H27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I27" s="3">
         <v>400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>100</v>
-      </c>
       <c r="W27" s="3">
+        <v>100</v>
+      </c>
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
         <v>0</v>
       </c>
@@ -2391,10 +2446,13 @@
         <v>0</v>
       </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,43 +2816,46 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2824,100 +2894,103 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-100</v>
       </c>
       <c r="G33" s="3">
         <v>-100</v>
       </c>
       <c r="H33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="3">
         <v>400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
-        <v>100</v>
-      </c>
       <c r="W33" s="3">
+        <v>100</v>
+      </c>
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
         <v>0</v>
       </c>
@@ -2925,10 +2998,13 @@
         <v>0</v>
       </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,86 +3092,89 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-100</v>
       </c>
       <c r="G35" s="3">
         <v>-100</v>
       </c>
       <c r="H35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I35" s="3">
         <v>400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
-        <v>100</v>
-      </c>
       <c r="W35" s="3">
+        <v>100</v>
+      </c>
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
         <v>0</v>
       </c>
@@ -3103,104 +3182,110 @@
         <v>0</v>
       </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E41" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="F41" s="3">
         <v>1100</v>
       </c>
       <c r="G41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L41" s="3">
+        <v>900</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O41" s="3">
+        <v>900</v>
+      </c>
+      <c r="P41" s="3">
         <v>1100</v>
       </c>
-      <c r="J41" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N41" s="3">
-        <v>900</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P41" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
-        <v>100</v>
-      </c>
       <c r="V41" s="3">
+        <v>100</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
-        <v>100</v>
-      </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
-        <v>100</v>
-      </c>
       <c r="Z41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
-        <v>100</v>
-      </c>
       <c r="AE41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3452,88 +3545,91 @@
         <v>700</v>
       </c>
       <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>800</v>
       </c>
       <c r="K43" s="3">
         <v>800</v>
       </c>
       <c r="L43" s="3">
+        <v>800</v>
+      </c>
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>800</v>
       </c>
       <c r="Q43" s="3">
         <v>800</v>
       </c>
       <c r="R43" s="3">
+        <v>800</v>
+      </c>
+      <c r="S43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>700</v>
       </c>
       <c r="Z43" s="3">
         <v>700</v>
       </c>
       <c r="AA43" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,17 +3729,17 @@
         <v>500</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
       <c r="I45" s="3">
         <v>100</v>
       </c>
@@ -3693,84 +3792,87 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
-        <v>100</v>
-      </c>
       <c r="AB45" s="3">
         <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2400</v>
       </c>
-      <c r="E46" s="3">
-        <v>2200</v>
-      </c>
       <c r="F46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I46" s="3">
         <v>2500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>2100</v>
       </c>
       <c r="J46" s="3">
         <v>2200</v>
       </c>
       <c r="K46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L46" s="3">
         <v>1700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
-      </c>
-      <c r="V46" s="3">
-        <v>1000</v>
       </c>
       <c r="W46" s="3">
         <v>1000</v>
@@ -3779,28 +3881,31 @@
         <v>1000</v>
       </c>
       <c r="Y46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3874,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="3">
         <v>200</v>
@@ -3885,11 +3990,14 @@
       <c r="AD47" s="3">
         <v>200</v>
       </c>
-      <c r="AE47" s="3" t="s">
+      <c r="AE47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3927,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>400</v>
@@ -3939,13 +4047,13 @@
         <v>400</v>
       </c>
       <c r="S48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T48" s="3">
         <v>300</v>
       </c>
       <c r="U48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4052,22 +4163,25 @@
         <v>0</v>
       </c>
       <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J54" s="3">
         <v>2200</v>
       </c>
-      <c r="F54" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H54" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1600</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1800</v>
       </c>
       <c r="O54" s="3">
         <v>1800</v>
       </c>
       <c r="P54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q54" s="3">
         <v>2100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1000</v>
       </c>
       <c r="V54" s="3">
         <v>1000</v>
       </c>
       <c r="W54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X54" s="3">
         <v>1100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5200</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>5500</v>
       </c>
       <c r="AD54" s="3">
         <v>5500</v>
       </c>
       <c r="AE54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AF54" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4589,11 +4720,11 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
@@ -4601,13 +4732,13 @@
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -4625,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
@@ -4640,22 +4771,22 @@
         <v>200</v>
       </c>
       <c r="W57" s="3">
+        <v>200</v>
+      </c>
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>200</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
@@ -4664,10 +4795,13 @@
         <v>200</v>
       </c>
       <c r="AE57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4680,8 +4814,8 @@
       <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+      <c r="G58" s="3">
+        <v>100</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
@@ -4689,8 +4823,8 @@
       <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4714,49 +4848,52 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>100</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>100</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
       </c>
       <c r="Y58" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>300</v>
       </c>
-      <c r="AD58" s="3">
-        <v>100</v>
-      </c>
       <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4764,25 +4901,25 @@
         <v>200</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
       </c>
       <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
         <v>200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>300</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
@@ -4794,19 +4931,19 @@
         <v>300</v>
       </c>
       <c r="O59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>200</v>
+      </c>
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>400</v>
       </c>
       <c r="T59" s="3">
         <v>400</v>
@@ -4815,11 +4952,11 @@
         <v>400</v>
       </c>
       <c r="V59" s="3">
+        <v>400</v>
+      </c>
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="W59" s="3">
-        <v>100</v>
-      </c>
       <c r="X59" s="3">
         <v>100</v>
       </c>
@@ -4830,13 +4967,13 @@
         <v>100</v>
       </c>
       <c r="AA59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3">
-        <v>100</v>
-      </c>
       <c r="AC59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD59" s="3">
         <v>200</v>
@@ -4844,97 +4981,103 @@
       <c r="AE59" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300</v>
+      </c>
+      <c r="E60" s="3">
         <v>400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
       </c>
       <c r="G60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H60" s="3">
         <v>300</v>
       </c>
       <c r="I60" s="3">
+        <v>300</v>
+      </c>
+      <c r="J60" s="3">
         <v>400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M60" s="3">
         <v>400</v>
       </c>
       <c r="N60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
       </c>
       <c r="P60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q60" s="3">
         <v>400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>500</v>
       </c>
       <c r="R60" s="3">
         <v>500</v>
       </c>
       <c r="S60" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T60" s="3">
         <v>600</v>
       </c>
       <c r="U60" s="3">
+        <v>600</v>
+      </c>
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4948,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -4972,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>400</v>
@@ -4984,14 +5127,14 @@
         <v>400</v>
       </c>
       <c r="S61" s="3">
+        <v>400</v>
+      </c>
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5069,8 +5215,8 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
@@ -5093,8 +5239,8 @@
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,8 +5533,11 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5387,7 +5545,7 @@
         <v>200</v>
       </c>
       <c r="E66" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F66" s="3">
         <v>400</v>
@@ -5402,10 +5560,10 @@
         <v>400</v>
       </c>
       <c r="J66" s="3">
+        <v>400</v>
+      </c>
+      <c r="K66" s="3">
         <v>300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>400</v>
       </c>
       <c r="L66" s="3">
         <v>400</v>
@@ -5417,58 +5575,61 @@
         <v>400</v>
       </c>
       <c r="O66" s="3">
+        <v>400</v>
+      </c>
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>800</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>900</v>
       </c>
       <c r="R66" s="3">
         <v>900</v>
       </c>
       <c r="S66" s="3">
+        <v>900</v>
+      </c>
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="I72" s="3">
         <v>-13700</v>
       </c>
-      <c r="E72" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-13700</v>
       </c>
-      <c r="G72" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-19400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-19700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-20700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-20100</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-19100</v>
       </c>
       <c r="W72" s="3">
         <v>-19100</v>
       </c>
       <c r="X72" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-19100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-18500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-14200</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>-13800</v>
       </c>
       <c r="AC72" s="3">
         <v>-13800</v>
       </c>
       <c r="AD72" s="3">
-        <v>-14300</v>
+        <v>-13800</v>
       </c>
       <c r="AE72" s="3">
         <v>-14300</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>-14300</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
-        <v>1800</v>
-      </c>
       <c r="F76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G76" s="3">
         <v>2100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2000</v>
       </c>
       <c r="H76" s="3">
         <v>2100</v>
       </c>
       <c r="I76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J76" s="3">
         <v>1700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>400</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
       <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3">
         <v>400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4800</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>5000</v>
       </c>
       <c r="AE76" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,180 +6579,186 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-100</v>
       </c>
       <c r="G81" s="3">
         <v>-100</v>
       </c>
       <c r="H81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="3">
         <v>400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
-        <v>100</v>
-      </c>
       <c r="W81" s="3">
+        <v>100</v>
+      </c>
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
         <v>0</v>
       </c>
@@ -6571,10 +6766,13 @@
         <v>0</v>
       </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6660,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -6678,13 +6877,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E89" s="3">
         <v>100</v>
       </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
-      </c>
-      <c r="O89" s="3">
-        <v>300</v>
       </c>
       <c r="P89" s="3">
         <v>300</v>
       </c>
       <c r="Q89" s="3">
+        <v>300</v>
+      </c>
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>100</v>
-      </c>
       <c r="AB89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC89" s="3">
         <v>700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7297,8 +7518,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
@@ -7309,8 +7530,8 @@
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7324,8 +7545,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
@@ -7333,26 +7554,29 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3">
-        <v>-300</v>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7601,25 +7831,28 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8055,49 +8301,52 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>200</v>
       </c>
       <c r="Z100" s="3">
         <v>200</v>
       </c>
       <c r="AA100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
-        <v>100</v>
-      </c>
       <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E102" s="3">
         <v>100</v>
       </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
-      </c>
-      <c r="O102" s="3">
-        <v>300</v>
       </c>
       <c r="P102" s="3">
         <v>300</v>
       </c>
       <c r="Q102" s="3">
+        <v>300</v>
+      </c>
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
-        <v>100</v>
-      </c>
       <c r="U102" s="3">
+        <v>100</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
       <c r="Y102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>LMDCF</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -797,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -815,19 +822,19 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
-        <v>100</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>100</v>
-      </c>
-      <c r="O8" s="3">
-        <v>800</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
@@ -839,49 +846,55 @@
         <v>100</v>
       </c>
       <c r="S8" s="3">
+        <v>800</v>
+      </c>
+      <c r="T8" s="3">
+        <v>100</v>
+      </c>
+      <c r="U8" s="3">
         <v>600</v>
       </c>
-      <c r="T8" s="3">
-        <v>100</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
-        <v>100</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="Z8" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -898,10 +911,10 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -910,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
@@ -922,40 +935,40 @@
         <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
@@ -970,10 +983,16 @@
         <v>100</v>
       </c>
       <c r="AF9" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -984,7 +1003,7 @@
         <v>700</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>700</v>
@@ -999,73 +1018,79 @@
         <v>100</v>
       </c>
       <c r="K10" s="3">
+        <v>700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>600</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <v>700</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>500</v>
       </c>
-      <c r="X10" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>700</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
         <v>500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>400</v>
       </c>
-      <c r="AF10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,73 +1140,73 @@
         <v>100</v>
       </c>
       <c r="G12" s="3">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>100</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3">
-        <v>100</v>
-      </c>
-      <c r="X12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>8</v>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,14 +1335,14 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>200</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1320,50 +1359,50 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>1600</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>1600</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1425,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1437,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1449,16 +1494,16 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD15" s="3">
         <v>300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>200</v>
       </c>
       <c r="AE15" s="3">
         <v>200</v>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,28 +1548,30 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E17" s="3">
         <v>400</v>
       </c>
       <c r="F17" s="3">
+        <v>300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>400</v>
+      </c>
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
-        <v>800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
       <c r="I17" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
@@ -1536,7 +1589,7 @@
         <v>300</v>
       </c>
       <c r="O17" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P17" s="3">
         <v>300</v>
@@ -1545,13 +1598,13 @@
         <v>200</v>
       </c>
       <c r="R17" s="3">
+        <v>300</v>
+      </c>
+      <c r="S17" s="3">
+        <v>200</v>
+      </c>
+      <c r="T17" s="3">
         <v>-100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>300</v>
-      </c>
-      <c r="T17" s="3">
-        <v>300</v>
       </c>
       <c r="U17" s="3">
         <v>300</v>
@@ -1560,37 +1613,43 @@
         <v>300</v>
       </c>
       <c r="W17" s="3">
+        <v>300</v>
+      </c>
+      <c r="X17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>600</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>400</v>
       </c>
       <c r="AE17" s="3">
         <v>600</v>
       </c>
       <c r="AF17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1657,97 @@
         <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H18" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I18" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-200</v>
       </c>
       <c r="K18" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="L18" s="3">
         <v>-200</v>
       </c>
       <c r="M18" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N18" s="3">
         <v>-200</v>
       </c>
       <c r="O18" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="P18" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="Q18" s="3">
         <v>600</v>
       </c>
       <c r="R18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S18" s="3">
+        <v>600</v>
+      </c>
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>500</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
       </c>
       <c r="W18" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="X18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>200</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,41 +1791,41 @@
         <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1793,22 +1860,28 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>100</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1819,22 +1892,22 @@
         <v>300</v>
       </c>
       <c r="F21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>600</v>
       </c>
       <c r="L21" s="3">
         <v>-200</v>
@@ -1843,64 +1916,70 @@
         <v>600</v>
       </c>
       <c r="N21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O21" s="3">
+        <v>600</v>
+      </c>
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>300</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U21" s="3">
-        <v>500</v>
       </c>
       <c r="V21" s="3">
         <v>-200</v>
       </c>
       <c r="W21" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="X21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1919,11 +1998,11 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1991,8 +2070,14 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2003,22 +2088,22 @@
         <v>300</v>
       </c>
       <c r="F23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>600</v>
       </c>
       <c r="L23" s="3">
         <v>-200</v>
@@ -2027,64 +2112,70 @@
         <v>600</v>
       </c>
       <c r="N23" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O23" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P23" s="3">
         <v>-300</v>
       </c>
       <c r="Q23" s="3">
+        <v>500</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U23" s="3">
-        <v>400</v>
       </c>
       <c r="V23" s="3">
         <v>-200</v>
       </c>
       <c r="W23" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>400</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB23" s="3">
         <v>-400</v>
       </c>
       <c r="AC23" s="3">
-        <v>100</v>
+        <v>-4300</v>
       </c>
       <c r="AD23" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,13 +2183,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -2134,49 +2225,55 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
       <c r="AC24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2364,14 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2279,31 +2382,31 @@
         <v>300</v>
       </c>
       <c r="F26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>600</v>
       </c>
       <c r="L26" s="3">
         <v>-200</v>
       </c>
       <c r="M26" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N26" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O26" s="3">
         <v>500</v>
@@ -2315,52 +2418,58 @@
         <v>500</v>
       </c>
       <c r="R26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S26" s="3">
+        <v>500</v>
+      </c>
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>100</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB26" s="3">
         <v>-400</v>
       </c>
       <c r="AC26" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="AD26" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
       <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2368,34 +2477,34 @@
         <v>-200</v>
       </c>
       <c r="E27" s="3">
+        <v>200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>600</v>
       </c>
       <c r="L27" s="3">
         <v>-200</v>
       </c>
       <c r="M27" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N27" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O27" s="3">
         <v>500</v>
@@ -2407,52 +2516,58 @@
         <v>500</v>
       </c>
       <c r="R27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S27" s="3">
+        <v>500</v>
+      </c>
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>100</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB27" s="3">
         <v>-400</v>
       </c>
       <c r="AC27" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="AD27" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE27" s="3">
         <v>0</v>
       </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,40 +2967,40 @@
         <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2897,22 +3036,28 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2920,34 +3065,34 @@
         <v>-200</v>
       </c>
       <c r="E33" s="3">
+        <v>200</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>600</v>
       </c>
       <c r="L33" s="3">
         <v>-200</v>
       </c>
       <c r="M33" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N33" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O33" s="3">
         <v>500</v>
@@ -2959,52 +3104,58 @@
         <v>500</v>
       </c>
       <c r="R33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>500</v>
+      </c>
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>100</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB33" s="3">
         <v>-400</v>
       </c>
       <c r="AC33" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="AD33" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE33" s="3">
         <v>0</v>
       </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3246,14 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3104,34 +3261,34 @@
         <v>-200</v>
       </c>
       <c r="E35" s="3">
+        <v>200</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>600</v>
       </c>
       <c r="L35" s="3">
         <v>-200</v>
       </c>
       <c r="M35" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N35" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O35" s="3">
         <v>500</v>
@@ -3143,149 +3300,161 @@
         <v>500</v>
       </c>
       <c r="R35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>500</v>
+      </c>
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>100</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB35" s="3">
         <v>-400</v>
       </c>
       <c r="AC35" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="AD35" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE35" s="3">
         <v>0</v>
       </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,67 +3523,69 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
-      </c>
-      <c r="O41" s="3">
-        <v>900</v>
-      </c>
-      <c r="P41" s="3">
-        <v>1100</v>
       </c>
       <c r="Q41" s="3">
         <v>900</v>
       </c>
       <c r="R41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S41" s="3">
+        <v>900</v>
+      </c>
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3">
-        <v>200</v>
-      </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
         <v>200</v>
@@ -3430,22 +3603,28 @@
         <v>200</v>
       </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3715,112 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>600</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1200</v>
       </c>
       <c r="H43" s="3">
         <v>800</v>
       </c>
       <c r="I43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>800</v>
+      </c>
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>800</v>
-      </c>
-      <c r="R43" s="3">
-        <v>800</v>
-      </c>
-      <c r="S43" s="3">
-        <v>700</v>
       </c>
       <c r="T43" s="3">
         <v>800</v>
       </c>
       <c r="U43" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="V43" s="3">
         <v>800</v>
       </c>
       <c r="W43" s="3">
+        <v>900</v>
+      </c>
+      <c r="X43" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y43" s="3">
         <v>700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1700</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>2300</v>
       </c>
       <c r="AF43" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,32 +3911,38 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
       <c r="K45" s="3">
         <v>100</v>
       </c>
@@ -3795,78 +3992,84 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>100</v>
-      </c>
       <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2600</v>
-      </c>
       <c r="H46" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="I46" s="3">
         <v>2500</v>
       </c>
       <c r="J46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L46" s="3">
         <v>2200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
-      </c>
-      <c r="P46" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>1700</v>
       </c>
       <c r="R46" s="3">
         <v>1400</v>
       </c>
       <c r="S46" s="3">
-        <v>1100</v>
+        <v>1700</v>
       </c>
       <c r="T46" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="U46" s="3">
         <v>1100</v>
@@ -3875,37 +4078,43 @@
         <v>900</v>
       </c>
       <c r="W46" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="X46" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Y46" s="3">
         <v>1000</v>
       </c>
       <c r="Z46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB46" s="3">
         <v>900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>2500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>2800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3982,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="AB47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="3">
         <v>200</v>
@@ -3993,11 +4202,17 @@
       <c r="AE47" s="3">
         <v>200</v>
       </c>
-      <c r="AF47" s="3" t="s">
+      <c r="AF47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4038,10 +4253,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
@@ -4050,17 +4265,17 @@
         <v>400</v>
       </c>
       <c r="T48" s="3">
+        <v>400</v>
+      </c>
+      <c r="U48" s="3">
+        <v>400</v>
+      </c>
+      <c r="V48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4166,22 +4387,28 @@
         <v>0</v>
       </c>
       <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
         <v>3000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>2800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>2400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,31 +4597,37 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F54" s="3">
         <v>2200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K54" s="3">
         <v>2600</v>
       </c>
-      <c r="H54" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1800</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>2100</v>
       </c>
       <c r="R54" s="3">
         <v>1800</v>
       </c>
       <c r="S54" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U54" s="3">
         <v>1500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1000</v>
-      </c>
-      <c r="W54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="X54" s="3">
-        <v>1100</v>
       </c>
       <c r="Y54" s="3">
         <v>1000</v>
       </c>
       <c r="Z54" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB54" s="3">
         <v>900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>5500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4967,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4723,28 +4984,28 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -4759,10 +5020,10 @@
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
@@ -4774,13 +5035,13 @@
         <v>200</v>
       </c>
       <c r="X57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z57" s="3">
         <v>500</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>400</v>
@@ -4789,24 +5050,30 @@
         <v>300</v>
       </c>
       <c r="AC57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AD57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE57" s="3">
         <v>200</v>
       </c>
       <c r="AF57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -4817,20 +5084,20 @@
       <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+      <c r="H58" s="3">
+        <v>100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>100</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4851,81 +5118,87 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
-      </c>
-      <c r="T58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>100</v>
+      </c>
+      <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3" t="s">
+      <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>100</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>100</v>
       </c>
       <c r="Y58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB58" s="3">
         <v>400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>300</v>
       </c>
-      <c r="AE58" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
       <c r="M59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
@@ -4934,35 +5207,35 @@
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>300</v>
       </c>
       <c r="T59" s="3">
         <v>400</v>
       </c>
       <c r="U59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V59" s="3">
         <v>400</v>
       </c>
       <c r="W59" s="3">
+        <v>400</v>
+      </c>
+      <c r="X59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="X59" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>100</v>
-      </c>
       <c r="Z59" s="3">
         <v>100</v>
       </c>
@@ -4970,7 +5243,7 @@
         <v>100</v>
       </c>
       <c r="AB59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
         <v>100</v>
@@ -4979,13 +5252,19 @@
         <v>200</v>
       </c>
       <c r="AE59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4993,91 +5272,97 @@
         <v>300</v>
       </c>
       <c r="E60" s="3">
+        <v>300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>300</v>
+      </c>
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>400</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
+        <v>400</v>
+      </c>
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
+        <v>300</v>
+      </c>
+      <c r="O60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
-      </c>
-      <c r="U60" s="3">
-        <v>600</v>
-      </c>
-      <c r="V60" s="3">
-        <v>800</v>
       </c>
       <c r="W60" s="3">
         <v>600</v>
       </c>
       <c r="X60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Y60" s="3">
         <v>600</v>
       </c>
       <c r="Z60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5094,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
@@ -5118,10 +5403,10 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>400</v>
@@ -5130,17 +5415,17 @@
         <v>400</v>
       </c>
       <c r="T61" s="3">
+        <v>400</v>
+      </c>
+      <c r="U61" s="3">
+        <v>400</v>
+      </c>
+      <c r="V61" s="3">
         <v>200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5218,11 +5509,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
@@ -5242,11 +5533,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5845,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5548,10 +5863,10 @@
         <v>200</v>
       </c>
       <c r="F66" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G66" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H66" s="3">
         <v>400</v>
@@ -5563,13 +5878,13 @@
         <v>400</v>
       </c>
       <c r="K66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L66" s="3">
         <v>400</v>
       </c>
       <c r="M66" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N66" s="3">
         <v>400</v>
@@ -5578,19 +5893,19 @@
         <v>400</v>
       </c>
       <c r="P66" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>400</v>
+      </c>
+      <c r="R66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>900</v>
-      </c>
-      <c r="S66" s="3">
-        <v>900</v>
-      </c>
-      <c r="T66" s="3">
-        <v>800</v>
       </c>
       <c r="U66" s="3">
         <v>900</v>
@@ -5599,37 +5914,43 @@
         <v>800</v>
       </c>
       <c r="W66" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="X66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Y66" s="3">
         <v>600</v>
       </c>
       <c r="Z66" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-14100</v>
+        <v>-13800</v>
       </c>
       <c r="E72" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-13900</v>
       </c>
-      <c r="F72" s="3">
-        <v>-14200</v>
-      </c>
       <c r="G72" s="3">
-        <v>-13900</v>
+        <v>-13700</v>
       </c>
       <c r="H72" s="3">
-        <v>-13800</v>
+        <v>-14000</v>
       </c>
       <c r="I72" s="3">
         <v>-13700</v>
       </c>
       <c r="J72" s="3">
-        <v>-14200</v>
+        <v>-13600</v>
       </c>
       <c r="K72" s="3">
         <v>-13700</v>
       </c>
       <c r="L72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="N72" s="3">
         <v>-14600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-14400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-14500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-14800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-15300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-19300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-19400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-19700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-20700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-20100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-19100</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-18100</v>
       </c>
       <c r="Z72" s="3">
         <v>-19100</v>
       </c>
       <c r="AA72" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-18500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-13800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M76" s="3">
         <v>1900</v>
       </c>
-      <c r="G76" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>900</v>
-      </c>
-      <c r="S76" s="3">
-        <v>600</v>
-      </c>
-      <c r="T76" s="3">
-        <v>300</v>
       </c>
       <c r="U76" s="3">
         <v>600</v>
       </c>
       <c r="V76" s="3">
+        <v>300</v>
+      </c>
+      <c r="W76" s="3">
+        <v>600</v>
+      </c>
+      <c r="X76" s="3">
         <v>200</v>
-      </c>
-      <c r="W76" s="3">
-        <v>400</v>
-      </c>
-      <c r="X76" s="3">
-        <v>300</v>
       </c>
       <c r="Y76" s="3">
         <v>400</v>
       </c>
       <c r="Z76" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AA76" s="3">
         <v>400</v>
       </c>
       <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD76" s="3">
         <v>4500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6959,117 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6688,34 +7077,34 @@
         <v>-200</v>
       </c>
       <c r="E81" s="3">
+        <v>200</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>600</v>
       </c>
       <c r="L81" s="3">
         <v>-200</v>
       </c>
       <c r="M81" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N81" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="O81" s="3">
         <v>500</v>
@@ -6727,52 +7116,58 @@
         <v>500</v>
       </c>
       <c r="R81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>500</v>
+      </c>
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>100</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-4300</v>
       </c>
       <c r="AB81" s="3">
         <v>-400</v>
       </c>
       <c r="AC81" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="AD81" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE81" s="3">
         <v>0</v>
       </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6862,13 +7259,13 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -6880,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>300</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>200</v>
       </c>
       <c r="AE83" s="3">
         <v>200</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>100</v>
-      </c>
       <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>300</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-200</v>
       </c>
       <c r="P89" s="3">
         <v>300</v>
       </c>
       <c r="Q89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R89" s="3">
         <v>300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>200</v>
       </c>
       <c r="S89" s="3">
         <v>300</v>
       </c>
       <c r="T89" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="U89" s="3">
         <v>300</v>
       </c>
       <c r="V89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
+        <v>300</v>
+      </c>
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE89" s="3">
         <v>700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7521,11 +7962,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
@@ -7533,11 +7974,11 @@
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -7548,35 +7989,41 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3" t="s">
+      <c r="AA91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3" t="s">
+      <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,16 +8212,22 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -7834,25 +8293,31 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-700</v>
       </c>
       <c r="AE94" s="3">
         <v>-500</v>
       </c>
       <c r="AF94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,13 +8738,19 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8304,49 +8795,55 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,64 +8934,70 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
-      <c r="F102" s="3">
-        <v>100</v>
-      </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
-      </c>
-      <c r="N102" s="3">
-        <v>300</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-200</v>
       </c>
       <c r="P102" s="3">
         <v>300</v>
       </c>
       <c r="Q102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R102" s="3">
         <v>300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>200</v>
       </c>
       <c r="S102" s="3">
         <v>300</v>
       </c>
       <c r="T102" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="U102" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V102" s="3">
         <v>-100</v>
@@ -8509,24 +9012,30 @@
         <v>100</v>
       </c>
       <c r="Z102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-200</v>
-      </c>
       <c r="AD102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE102" s="3">
         <v>-200</v>
       </c>
       <c r="AF102" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LMDCF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>LMDCF</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>700</v>
       </c>
       <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
       <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
-        <v>100</v>
-      </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
-        <v>100</v>
-      </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
-        <v>100</v>
-      </c>
       <c r="M8" s="3">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
-        <v>100</v>
-      </c>
       <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="P8" s="3">
-        <v>100</v>
-      </c>
       <c r="Q8" s="3">
+        <v>100</v>
+      </c>
+      <c r="R8" s="3">
         <v>800</v>
       </c>
-      <c r="R8" s="3">
-        <v>100</v>
-      </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
         <v>800</v>
       </c>
-      <c r="T8" s="3">
-        <v>100</v>
-      </c>
       <c r="U8" s="3">
+        <v>100</v>
+      </c>
+      <c r="V8" s="3">
         <v>600</v>
       </c>
-      <c r="V8" s="3">
-        <v>100</v>
-      </c>
       <c r="W8" s="3">
+        <v>100</v>
+      </c>
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
-        <v>100</v>
-      </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>700</v>
       </c>
-      <c r="AB8" s="3">
-        <v>100</v>
-      </c>
       <c r="AC8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD8" s="3">
         <v>600</v>
       </c>
-      <c r="AD8" s="3">
-        <v>300</v>
-      </c>
       <c r="AE8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF8" s="3">
         <v>800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -917,7 +924,7 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -929,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
@@ -941,19 +948,19 @@
         <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
@@ -962,135 +969,141 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3">
         <v>100</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>700</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
       <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
       <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>700</v>
       </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
-        <v>100</v>
-      </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>700</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>600</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
         <v>700</v>
       </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
       <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>500</v>
       </c>
-      <c r="Z10" s="3">
-        <v>100</v>
-      </c>
       <c r="AA10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB10" s="3">
         <v>700</v>
       </c>
-      <c r="AB10" s="3">
-        <v>0</v>
-      </c>
       <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
         <v>500</v>
       </c>
-      <c r="AD10" s="3">
-        <v>300</v>
-      </c>
       <c r="AE10" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF10" s="3">
         <v>800</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>400</v>
       </c>
       <c r="AG10" s="3">
         <v>400</v>
       </c>
       <c r="AH10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1149,34 +1163,34 @@
         <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>0</v>
       </c>
       <c r="Q12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -1194,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
@@ -1203,13 +1217,13 @@
         <v>100</v>
       </c>
       <c r="AB12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>8</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1341,11 +1361,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1365,23 +1385,23 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1389,11 +1409,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1401,11 +1421,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1476,16 +1499,16 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1500,13 +1523,13 @@
         <v>0</v>
       </c>
       <c r="AC15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF15" s="3">
         <v>200</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1562,19 +1589,19 @@
         <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G17" s="3">
+        <v>300</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="I17" s="3">
-        <v>700</v>
-      </c>
       <c r="J17" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
@@ -1595,20 +1622,20 @@
         <v>300</v>
       </c>
       <c r="Q17" s="3">
+        <v>300</v>
+      </c>
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
-        <v>300</v>
-      </c>
       <c r="S17" s="3">
+        <v>300</v>
+      </c>
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-100</v>
       </c>
-      <c r="U17" s="3">
-        <v>300</v>
-      </c>
       <c r="V17" s="3">
         <v>300</v>
       </c>
@@ -1619,135 +1646,141 @@
         <v>300</v>
       </c>
       <c r="Y17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3">
-        <v>300</v>
-      </c>
       <c r="AB17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4900</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>600</v>
       </c>
       <c r="AE17" s="3">
         <v>600</v>
       </c>
       <c r="AF17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG17" s="3">
         <v>400</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>600</v>
       </c>
       <c r="AH17" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>300</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
-        <v>300</v>
-      </c>
       <c r="H18" s="3">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
-        <v>300</v>
-      </c>
       <c r="V18" s="3">
+        <v>300</v>
+      </c>
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
       <c r="Z18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
       <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,53 +1815,54 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1866,120 +1900,126 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>-100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>300</v>
       </c>
       <c r="E21" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="F21" s="3">
+        <v>300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
-        <v>300</v>
-      </c>
       <c r="H21" s="3">
+        <v>300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-100</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>200</v>
       </c>
-      <c r="U21" s="3">
-        <v>300</v>
-      </c>
       <c r="V21" s="3">
+        <v>300</v>
+      </c>
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
-        <v>100</v>
-      </c>
       <c r="Z21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>200</v>
       </c>
       <c r="AG21" s="3">
         <v>200</v>
       </c>
       <c r="AH21" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2004,8 +2044,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2076,117 +2116,123 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
-        <v>300</v>
-      </c>
       <c r="F23" s="3">
+        <v>300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>300</v>
-      </c>
       <c r="H23" s="3">
+        <v>300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-100</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
-        <v>300</v>
-      </c>
       <c r="V23" s="3">
+        <v>300</v>
+      </c>
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>100</v>
-      </c>
       <c r="Z23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
-        <v>100</v>
-      </c>
       <c r="AF23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG23" s="3">
         <v>0</v>
       </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -2195,40 +2241,40 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2237,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2249,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2261,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="AE24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,95 +2419,98 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
-        <v>300</v>
-      </c>
       <c r="F26" s="3">
+        <v>300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>300</v>
-      </c>
       <c r="H26" s="3">
+        <v>300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
-        <v>300</v>
-      </c>
       <c r="V26" s="3">
+        <v>300</v>
+      </c>
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>100</v>
-      </c>
       <c r="Z26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>300</v>
-      </c>
       <c r="AB26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
@@ -2466,97 +2518,100 @@
         <v>0</v>
       </c>
       <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
-        <v>200</v>
-      </c>
       <c r="F27" s="3">
+        <v>300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
-        <v>300</v>
-      </c>
       <c r="H27" s="3">
+        <v>300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-100</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
       </c>
       <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
-        <v>300</v>
-      </c>
       <c r="V27" s="3">
+        <v>300</v>
+      </c>
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>100</v>
-      </c>
       <c r="Z27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>300</v>
-      </c>
       <c r="AB27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
         <v>0</v>
       </c>
@@ -2564,10 +2619,13 @@
         <v>0</v>
       </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,52 +3025,55 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3042,109 +3112,112 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
-        <v>200</v>
-      </c>
       <c r="F33" s="3">
+        <v>300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
-        <v>300</v>
-      </c>
       <c r="H33" s="3">
+        <v>300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-100</v>
       </c>
       <c r="J33" s="3">
         <v>-100</v>
       </c>
       <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
-        <v>300</v>
-      </c>
       <c r="V33" s="3">
+        <v>300</v>
+      </c>
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>100</v>
-      </c>
       <c r="Z33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>300</v>
-      </c>
       <c r="AB33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
         <v>0</v>
       </c>
@@ -3152,10 +3225,13 @@
         <v>0</v>
       </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,95 +3328,98 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
-        <v>200</v>
-      </c>
       <c r="F35" s="3">
+        <v>300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
-        <v>300</v>
-      </c>
       <c r="H35" s="3">
+        <v>300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-100</v>
       </c>
       <c r="J35" s="3">
         <v>-100</v>
       </c>
       <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
-        <v>300</v>
-      </c>
       <c r="V35" s="3">
+        <v>300</v>
+      </c>
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>100</v>
-      </c>
       <c r="Z35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>300</v>
-      </c>
       <c r="AB35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
         <v>0</v>
       </c>
@@ -3348,113 +3427,119 @@
         <v>0</v>
       </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
-        <v>1200</v>
-      </c>
       <c r="H41" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="I41" s="3">
         <v>1100</v>
       </c>
       <c r="J41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="U41" s="3">
-        <v>300</v>
-      </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
-        <v>100</v>
-      </c>
       <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
-        <v>100</v>
-      </c>
       <c r="AA41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
-        <v>100</v>
-      </c>
       <c r="AC41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG41" s="3">
         <v>200</v>
       </c>
-      <c r="AG41" s="3">
-        <v>100</v>
-      </c>
       <c r="AH41" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>700</v>
       </c>
       <c r="G43" s="3">
         <v>700</v>
       </c>
       <c r="H43" s="3">
+        <v>700</v>
+      </c>
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
-      </c>
-      <c r="M43" s="3">
-        <v>800</v>
       </c>
       <c r="N43" s="3">
         <v>800</v>
       </c>
       <c r="O43" s="3">
+        <v>800</v>
+      </c>
+      <c r="P43" s="3">
         <v>900</v>
       </c>
-      <c r="P43" s="3">
-        <v>300</v>
-      </c>
       <c r="Q43" s="3">
+        <v>300</v>
+      </c>
+      <c r="R43" s="3">
         <v>700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
-      </c>
-      <c r="S43" s="3">
-        <v>800</v>
       </c>
       <c r="T43" s="3">
         <v>800</v>
       </c>
       <c r="U43" s="3">
+        <v>800</v>
+      </c>
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>800</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>700</v>
       </c>
       <c r="AC43" s="3">
         <v>700</v>
       </c>
       <c r="AD43" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE43" s="3">
         <v>1600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3929,23 +4028,23 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>500</v>
       </c>
       <c r="H45" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
       </c>
       <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
-        <v>100</v>
-      </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
@@ -3998,93 +4097,96 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>100</v>
-      </c>
       <c r="AE45" s="3">
         <v>100</v>
       </c>
       <c r="AF45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AG45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2000</v>
-      </c>
-      <c r="E46" s="3">
-        <v>2200</v>
       </c>
       <c r="F46" s="3">
         <v>2200</v>
       </c>
       <c r="G46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H46" s="3">
         <v>2400</v>
       </c>
-      <c r="H46" s="3">
-        <v>2200</v>
-      </c>
       <c r="I46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L46" s="3">
         <v>2500</v>
-      </c>
-      <c r="J46" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L46" s="3">
-        <v>2200</v>
       </c>
       <c r="M46" s="3">
         <v>2200</v>
       </c>
       <c r="N46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O46" s="3">
         <v>1700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>900</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1000</v>
       </c>
       <c r="Z46" s="3">
         <v>1000</v>
@@ -4093,28 +4195,31 @@
         <v>1000</v>
       </c>
       <c r="AB46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC46" s="3">
         <v>900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4197,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE47" s="3">
         <v>200</v>
@@ -4208,11 +4313,14 @@
       <c r="AG47" s="3">
         <v>200</v>
       </c>
-      <c r="AH47" s="3" t="s">
+      <c r="AH47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4259,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
@@ -4271,13 +4379,13 @@
         <v>400</v>
       </c>
       <c r="V48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>300</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4393,22 +4504,25 @@
         <v>0</v>
       </c>
       <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
         <v>3000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4614,8 +4734,8 @@
       <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
+      <c r="F52" s="3">
+        <v>300</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
@@ -4629,8 +4749,8 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2300</v>
       </c>
-      <c r="I54" s="3">
-        <v>2500</v>
-      </c>
       <c r="J54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K54" s="3">
         <v>2400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>1800</v>
       </c>
       <c r="R54" s="3">
         <v>1800</v>
       </c>
       <c r="S54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T54" s="3">
         <v>2100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1400</v>
-      </c>
-      <c r="X54" s="3">
-        <v>1000</v>
       </c>
       <c r="Y54" s="3">
         <v>1000</v>
       </c>
       <c r="Z54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA54" s="3">
         <v>1100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5200</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>5500</v>
       </c>
       <c r="AG54" s="3">
         <v>5500</v>
       </c>
       <c r="AH54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AI54" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,13 +5099,14 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -4990,11 +5121,11 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
@@ -5002,13 +5133,13 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -5026,7 +5157,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
@@ -5041,22 +5172,22 @@
         <v>200</v>
       </c>
       <c r="Z57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
-        <v>300</v>
-      </c>
       <c r="AC57" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
-        <v>300</v>
-      </c>
       <c r="AE57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF57" s="3">
         <v>200</v>
@@ -5065,10 +5196,13 @@
         <v>200</v>
       </c>
       <c r="AH57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5076,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -5090,8 +5224,8 @@
       <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -5099,8 +5233,8 @@
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5124,49 +5258,52 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>100</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>100</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
       </c>
       <c r="AB58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC58" s="3">
         <v>400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>200</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
       <c r="AF58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AH58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5174,7 +5311,7 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -5183,26 +5320,26 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J59" s="3">
         <v>200</v>
       </c>
       <c r="K59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
       <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
-        <v>300</v>
-      </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
@@ -5213,19 +5350,19 @@
         <v>300</v>
       </c>
       <c r="R59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S59" s="3">
         <v>200</v>
       </c>
       <c r="T59" s="3">
+        <v>200</v>
+      </c>
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
-        <v>300</v>
-      </c>
       <c r="V59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W59" s="3">
         <v>400</v>
@@ -5234,10 +5371,10 @@
         <v>400</v>
       </c>
       <c r="Y59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA59" s="3">
         <v>100</v>
@@ -5249,13 +5386,13 @@
         <v>100</v>
       </c>
       <c r="AD59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AE59" s="3">
-        <v>100</v>
-      </c>
       <c r="AF59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG59" s="3">
         <v>200</v>
@@ -5263,106 +5400,112 @@
       <c r="AH59" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>300</v>
       </c>
       <c r="G60" s="3">
+        <v>300</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>500</v>
       </c>
       <c r="I60" s="3">
         <v>500</v>
       </c>
       <c r="J60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
+        <v>300</v>
+      </c>
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="M60" s="3">
-        <v>300</v>
-      </c>
       <c r="N60" s="3">
         <v>300</v>
       </c>
       <c r="O60" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P60" s="3">
         <v>400</v>
       </c>
       <c r="Q60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
       </c>
       <c r="S60" s="3">
+        <v>300</v>
+      </c>
+      <c r="T60" s="3">
         <v>400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>500</v>
       </c>
       <c r="U60" s="3">
         <v>500</v>
       </c>
       <c r="V60" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W60" s="3">
         <v>600</v>
       </c>
       <c r="X60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>400</v>
       </c>
-      <c r="AE60" s="3">
-        <v>300</v>
-      </c>
       <c r="AF60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG60" s="3">
         <v>700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5385,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
@@ -5409,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>400</v>
@@ -5421,13 +5564,13 @@
         <v>400</v>
       </c>
       <c r="V61" s="3">
+        <v>400</v>
+      </c>
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
-        <v>300</v>
-      </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5515,8 +5661,8 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
@@ -5539,8 +5685,8 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,13 +6006,16 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E66" s="3">
         <v>200</v>
@@ -5869,7 +6027,7 @@
         <v>200</v>
       </c>
       <c r="H66" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I66" s="3">
         <v>400</v>
@@ -5884,10 +6042,10 @@
         <v>400</v>
       </c>
       <c r="M66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N66" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O66" s="3">
         <v>400</v>
@@ -5899,58 +6057,61 @@
         <v>400</v>
       </c>
       <c r="R66" s="3">
+        <v>400</v>
+      </c>
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>800</v>
-      </c>
-      <c r="T66" s="3">
-        <v>900</v>
       </c>
       <c r="U66" s="3">
         <v>900</v>
       </c>
       <c r="V66" s="3">
+        <v>900</v>
+      </c>
+      <c r="W66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>400</v>
       </c>
-      <c r="AE66" s="3">
-        <v>300</v>
-      </c>
       <c r="AF66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG66" s="3">
         <v>700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="H72" s="3">
         <v>-13800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-13600</v>
       </c>
-      <c r="F72" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="L72" s="3">
         <v>-13700</v>
       </c>
-      <c r="H72" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="N72" s="3">
         <v>-13700</v>
       </c>
-      <c r="J72" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-15700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-15300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-19300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-19400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-19700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-20700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-20100</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-19100</v>
       </c>
       <c r="Z72" s="3">
         <v>-19100</v>
       </c>
       <c r="AA72" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-19100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-18500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-14200</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-13800</v>
       </c>
       <c r="AF72" s="3">
         <v>-13800</v>
       </c>
       <c r="AG72" s="3">
-        <v>-14300</v>
+        <v>-13800</v>
       </c>
       <c r="AH72" s="3">
         <v>-14300</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-14300</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2200</v>
       </c>
-      <c r="H76" s="3">
-        <v>1800</v>
-      </c>
       <c r="I76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J76" s="3">
         <v>2100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>600</v>
       </c>
-      <c r="V76" s="3">
-        <v>300</v>
-      </c>
       <c r="W76" s="3">
+        <v>300</v>
+      </c>
+      <c r="X76" s="3">
         <v>600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>400</v>
       </c>
-      <c r="Z76" s="3">
-        <v>300</v>
-      </c>
       <c r="AA76" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB76" s="3">
         <v>400</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
-      </c>
       <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3">
         <v>400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4800</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>5000</v>
       </c>
       <c r="AH76" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,198 +7154,204 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
-        <v>200</v>
-      </c>
       <c r="F81" s="3">
+        <v>300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
-        <v>300</v>
-      </c>
       <c r="H81" s="3">
+        <v>300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-100</v>
       </c>
       <c r="J81" s="3">
         <v>-100</v>
       </c>
       <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
-        <v>300</v>
-      </c>
       <c r="V81" s="3">
+        <v>300</v>
+      </c>
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>100</v>
-      </c>
       <c r="Z81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>300</v>
-      </c>
       <c r="AB81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
         <v>0</v>
       </c>
@@ -7164,10 +7359,13 @@
         <v>0</v>
       </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7265,10 +7464,10 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -7283,13 +7482,13 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
+        <v>300</v>
+      </c>
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>100</v>
-      </c>
       <c r="H89" s="3">
         <v>100</v>
       </c>
       <c r="I89" s="3">
+        <v>100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
-        <v>300</v>
-      </c>
       <c r="Q89" s="3">
+        <v>300</v>
+      </c>
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
-        <v>300</v>
-      </c>
       <c r="S89" s="3">
         <v>300</v>
       </c>
       <c r="T89" s="3">
+        <v>300</v>
+      </c>
+      <c r="U89" s="3">
         <v>200</v>
       </c>
-      <c r="U89" s="3">
-        <v>300</v>
-      </c>
       <c r="V89" s="3">
+        <v>300</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
-        <v>300</v>
-      </c>
       <c r="X89" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
-        <v>100</v>
-      </c>
       <c r="AE89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF89" s="3">
         <v>700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7968,8 +8189,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
@@ -7980,8 +8201,8 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7995,8 +8216,8 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -8004,26 +8225,29 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG91" s="3">
-        <v>-300</v>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,20 +8445,23 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -8299,25 +8529,28 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>1400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,17 +8987,20 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -8801,49 +9047,52 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>200</v>
       </c>
       <c r="AC100" s="3">
         <v>200</v>
       </c>
       <c r="AD100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>200</v>
       </c>
-      <c r="AG100" s="3">
-        <v>100</v>
-      </c>
       <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
-        <v>100</v>
-      </c>
       <c r="H102" s="3">
         <v>100</v>
       </c>
       <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
-        <v>300</v>
-      </c>
       <c r="Q102" s="3">
+        <v>300</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
-        <v>300</v>
-      </c>
       <c r="S102" s="3">
         <v>300</v>
       </c>
       <c r="T102" s="3">
+        <v>300</v>
+      </c>
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
-        <v>300</v>
-      </c>
       <c r="V102" s="3">
+        <v>300</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>100</v>
-      </c>
       <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-900</v>
       </c>
     </row>
